--- a/data/trans_camb/P16A11-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A11-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,82</t>
+          <t>0,33; 8,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 4,86</t>
+          <t>-3,07; 4,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,6</t>
+          <t>2,86; 10,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 11,74</t>
+          <t>3,53; 11,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 7,24</t>
+          <t>-1,21; 7,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,52</t>
+          <t>3,11; 10,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 8,8</t>
+          <t>3,35; 9,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,72</t>
+          <t>-0,7; 4,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,13; 9,41</t>
+          <t>4,31; 9,36</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 70,67</t>
+          <t>1,82; 66,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 38,98</t>
+          <t>-18,86; 35,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,61; 82,29</t>
+          <t>17,12; 81,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,36; 80,71</t>
+          <t>17,98; 79,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 47,62</t>
+          <t>-5,93; 47,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,13; 72,84</t>
+          <t>16,11; 71,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,57; 63,24</t>
+          <t>19,73; 65,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 34,18</t>
+          <t>-4,08; 35,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,82; 67,74</t>
+          <t>25,1; 67,97</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 5,39</t>
+          <t>-1,05; 5,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 4,69</t>
+          <t>-1,51; 4,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 5,06</t>
+          <t>-6,46; 5,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 4,59</t>
+          <t>-2,42; 4,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 2,65</t>
+          <t>-4,08; 2,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 4,04</t>
+          <t>-1,95; 4,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,85</t>
+          <t>-0,61; 4,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,75</t>
+          <t>-1,99; 2,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 3,36</t>
+          <t>-5,42; 3,52</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 47,63</t>
+          <t>-7,55; 45,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 41,85</t>
+          <t>-10,33; 42,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-45,74; 42,75</t>
+          <t>-48,73; 42,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 29,57</t>
+          <t>-12,69; 29,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 17,37</t>
+          <t>-20,87; 18,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 26,38</t>
+          <t>-9,97; 25,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 27,95</t>
+          <t>-4,1; 28,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 19,87</t>
+          <t>-12,49; 19,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,54; 23,53</t>
+          <t>-32,34; 24,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 6,3</t>
+          <t>-1,83; 5,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 5,71</t>
+          <t>-1,75; 5,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 10,79</t>
+          <t>2,68; 10,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 4,56</t>
+          <t>-3,22; 4,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 5,46</t>
+          <t>-2,09; 5,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 48,87</t>
+          <t>-2,22; 53,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 4,23</t>
+          <t>-1,33; 4,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 4,52</t>
+          <t>-1,13; 4,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 40,45</t>
+          <t>2,23; 35,44</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 55,63</t>
+          <t>-12,23; 53,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 51,81</t>
+          <t>-11,94; 52,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,56; 98,08</t>
+          <t>17,36; 99,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 30,73</t>
+          <t>-17,72; 34,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 37,03</t>
+          <t>-11,19; 40,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 341,74</t>
+          <t>-12,8; 319,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 32,65</t>
+          <t>-8,64; 30,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 34,62</t>
+          <t>-6,91; 33,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,52; 276,74</t>
+          <t>14,61; 264,88</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,64; 10,16</t>
+          <t>3,87; 10,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 7,01</t>
+          <t>0,7; 6,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,39; 11,64</t>
+          <t>5,5; 11,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 11,55</t>
+          <t>4,31; 11,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 4,74</t>
+          <t>-2,24; 4,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 10,07</t>
+          <t>1,56; 10,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,72</t>
+          <t>4,97; 10,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,03</t>
+          <t>0,19; 4,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,89</t>
+          <t>4,42; 9,71</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>27,44; 100,95</t>
+          <t>30,52; 106,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,36; 71,1</t>
+          <t>5,82; 71,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43,82; 118,35</t>
+          <t>42,34; 114,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23,49; 82,44</t>
+          <t>26,03; 78,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 34,06</t>
+          <t>-13,42; 32,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,15; 71,86</t>
+          <t>9,2; 70,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,72; 77,03</t>
+          <t>33,48; 78,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,48; 40,54</t>
+          <t>1,18; 37,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33,77; 78,86</t>
+          <t>31,23; 77,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,78</t>
+          <t>2,4; 5,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,95</t>
+          <t>0,6; 3,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,31</t>
+          <t>1,29; 7,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,17</t>
+          <t>2,32; 6,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,84</t>
+          <t>-0,78; 2,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,9; 22,26</t>
+          <t>2,81; 20,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,4</t>
+          <t>2,89; 5,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,99</t>
+          <t>0,35; 2,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,66; 15,42</t>
+          <t>3,64; 16,87</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>16,44; 48,97</t>
+          <t>17,27; 48,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,64; 33,87</t>
+          <t>4,52; 33,01</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,22; 60,54</t>
+          <t>11,63; 58,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14,19; 39,59</t>
+          <t>13,53; 38,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 18,31</t>
+          <t>-4,44; 18,79</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,27; 129,5</t>
+          <t>16,33; 128,3</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,59; 38,31</t>
+          <t>18,72; 39,13</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,54; 21,34</t>
+          <t>2,43; 20,28</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>24,12; 103,79</t>
+          <t>24,26; 116,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A11-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A11-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,67</t>
+          <t>6,51</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>6,2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,72</t>
+          <t>6,39</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 8,34</t>
+          <t>0,93; 8,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 4,4</t>
+          <t>-2,57; 4,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 10,3</t>
+          <t>2,42; 10,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 11,78</t>
+          <t>3,26; 11,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 7,0</t>
+          <t>-1,56; 6,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 10,26</t>
+          <t>2,41; 9,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 9,25</t>
+          <t>3,32; 9,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,93</t>
+          <t>-0,77; 5,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 9,36</t>
+          <t>3,67; 9,07</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 66,85</t>
+          <t>5,27; 69,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 35,42</t>
+          <t>-15,89; 35,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,12; 81,88</t>
+          <t>15,07; 82,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,98; 79,18</t>
+          <t>16,67; 78,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 47,01</t>
+          <t>-7,57; 47,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,11; 71,06</t>
+          <t>11,39; 64,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,73; 65,94</t>
+          <t>20,12; 65,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 35,41</t>
+          <t>-5,03; 36,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,1; 67,97</t>
+          <t>21,59; 64,78</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>2,49</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 5,21</t>
+          <t>-0,85; 5,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,78</t>
+          <t>-1,14; 5,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 5,19</t>
+          <t>0,94; 6,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 4,6</t>
+          <t>-2,61; 4,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 2,94</t>
+          <t>-4,15; 2,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 4,16</t>
+          <t>-2,4; 4,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 4,1</t>
+          <t>-0,68; 4,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,74</t>
+          <t>-2,04; 2,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 3,52</t>
+          <t>0,21; 4,69</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 45,83</t>
+          <t>-5,6; 48,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 42,77</t>
+          <t>-8,6; 47,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,73; 42,44</t>
+          <t>6,9; 62,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 29,55</t>
+          <t>-12,87; 28,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,87; 18,11</t>
+          <t>-21,38; 18,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 25,72</t>
+          <t>-11,52; 26,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 28,85</t>
+          <t>-4,32; 29,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 19,24</t>
+          <t>-12,6; 19,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 24,36</t>
+          <t>1,5; 34,93</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,74</t>
+          <t>6,75</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,64</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,24</t>
+          <t>3,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 5,68</t>
+          <t>-1,46; 6,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 5,61</t>
+          <t>-2,24; 5,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 10,85</t>
+          <t>2,83; 10,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,93</t>
+          <t>-3,37; 4,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 5,82</t>
+          <t>-2,4; 5,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 53,37</t>
+          <t>-3,23; 3,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,23</t>
+          <t>-1,0; 4,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 4,57</t>
+          <t>-0,94; 4,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 35,44</t>
+          <t>0,82; 5,83</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>104,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 53,89</t>
+          <t>-10,54; 57,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 52,84</t>
+          <t>-14,59; 46,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,36; 99,18</t>
+          <t>19,0; 98,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,72; 34,13</t>
+          <t>-18,22; 28,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 40,38</t>
+          <t>-13,05; 39,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 319,29</t>
+          <t>-16,96; 24,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 30,86</t>
+          <t>-6,02; 32,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 33,98</t>
+          <t>-5,81; 33,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,61; 264,88</t>
+          <t>4,76; 42,96</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,56</t>
+          <t>7,84</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,66</t>
+          <t>7,69</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,6</t>
+          <t>7,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 10,44</t>
+          <t>3,61; 10,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,98</t>
+          <t>0,95; 6,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 11,6</t>
+          <t>5,02; 11,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,31; 11,06</t>
+          <t>4,05; 11,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 4,76</t>
+          <t>-1,77; 4,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 10,02</t>
+          <t>4,63; 10,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,97; 10,1</t>
+          <t>5,04; 9,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,67</t>
+          <t>0,17; 4,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,42; 9,71</t>
+          <t>5,75; 10,02</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30,52; 106,64</t>
+          <t>29,12; 101,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,82; 71,45</t>
+          <t>7,73; 67,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42,34; 114,96</t>
+          <t>38,33; 109,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26,03; 78,52</t>
+          <t>23,24; 78,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 32,68</t>
+          <t>-10,04; 34,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,2; 70,25</t>
+          <t>25,47; 73,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,48; 78,89</t>
+          <t>33,91; 78,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,18; 37,41</t>
+          <t>1,13; 39,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,23; 77,18</t>
+          <t>38,5; 81,0</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>3,86</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>5,0</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,79</t>
+          <t>2,32; 5,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,95</t>
+          <t>0,48; 3,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,11</t>
+          <t>4,5; 7,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,05</t>
+          <t>2,29; 6,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,94</t>
+          <t>-0,86; 2,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,81; 20,6</t>
+          <t>2,37; 5,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,53</t>
+          <t>2,83; 5,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,84</t>
+          <t>0,34; 2,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,64; 16,87</t>
+          <t>3,76; 6,2</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>17,27; 48,24</t>
+          <t>16,86; 48,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,52; 33,01</t>
+          <t>3,62; 31,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11,63; 58,49</t>
+          <t>32,88; 66,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,53; 38,73</t>
+          <t>12,75; 38,66</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 18,79</t>
+          <t>-4,96; 18,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,33; 128,3</t>
+          <t>13,31; 34,9</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,72; 39,13</t>
+          <t>18,51; 38,89</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,43; 20,28</t>
+          <t>2,18; 21,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>24,26; 116,96</t>
+          <t>24,8; 44,47</t>
         </is>
       </c>
     </row>
